--- a/BeatnotePostHotCellF1=4/Jun30,2026/Fit_ResultJun30.xlsx
+++ b/BeatnotePostHotCellF1=4/Jun30,2026/Fit_ResultJun30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCellF1=4\Jun30,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616B1204-69D2-4E28-891F-1F6134148DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{711BA157-ADF1-408A-B7B4-2494EA6AFDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="4470" yWindow="3300" windowWidth="21600" windowHeight="11295" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="AbsCoef" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -594,15 +595,30 @@
       <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:22" ht="42.75">
       <c r="A2" s="1" t="s">
@@ -627,15 +643,39 @@
         <v>3.1532650443772902E-3</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="I2">
+        <f>AVERAGE(B2:B33)</f>
+        <v>14.765901901229174</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1">
+        <v>14.6522889999402</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3689540908806099</v>
+      </c>
+      <c r="O2" s="1">
+        <v>-3.7700736037058098E-3</v>
+      </c>
+      <c r="P2" s="1">
+        <v>5.1784265669725996E-4</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>2.3753749195829301</v>
+      </c>
+      <c r="R2" s="1">
+        <v>42.084666143904002</v>
+      </c>
+      <c r="S2" s="1">
+        <v>3.3244935994686999E-3</v>
+      </c>
       <c r="T2" s="1"/>
+      <c r="U2">
+        <f>AVERAGE(M2:M33)</f>
+        <v>14.76427315563798</v>
+      </c>
     </row>
     <row r="3" spans="1:22" ht="42.75">
       <c r="A3" s="1" t="s">
@@ -660,8 +700,39 @@
         <v>3.28395375425622E-3</v>
       </c>
       <c r="H3" s="1"/>
+      <c r="I3">
+        <f>_xlfn.STDEV.S(B2:B33)</f>
+        <v>0.14091053733310865</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="1">
+        <v>14.9257190945536</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1.36897061106933</v>
+      </c>
+      <c r="O3" s="1">
+        <v>-3.78568823181624E-3</v>
+      </c>
+      <c r="P3" s="1">
+        <v>4.7518718847408098E-4</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>2.3759329710563599</v>
+      </c>
+      <c r="R3" s="1">
+        <v>40.060511420041301</v>
+      </c>
+      <c r="S3" s="1">
+        <v>3.1944488826405101E-3</v>
+      </c>
       <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
+      <c r="U3">
+        <f>_xlfn.STDEV.S(M2:M33)</f>
+        <v>0.11723666583628554</v>
+      </c>
       <c r="V3" s="1"/>
     </row>
     <row r="4" spans="1:22" ht="42.75">
@@ -687,7 +758,39 @@
         <v>3.57139192202735E-3</v>
       </c>
       <c r="H4" s="1"/>
+      <c r="I4">
+        <f>I3/I2</f>
+        <v>9.5429685416898707E-3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="1">
+        <v>14.7998869819949</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1.3697383123965801</v>
+      </c>
+      <c r="O4" s="1">
+        <v>-3.68073907311563E-3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>3.7029655679784502E-4</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>2.3745710339381501</v>
+      </c>
+      <c r="R4" s="1">
+        <v>40.077035520837498</v>
+      </c>
+      <c r="S4" s="1">
+        <v>3.1727979703080498E-3</v>
+      </c>
       <c r="T4" s="1"/>
+      <c r="U4">
+        <f>U3/U2</f>
+        <v>7.9405646726006824E-3</v>
+      </c>
     </row>
     <row r="5" spans="1:22" ht="42.75">
       <c r="A5" s="1" t="s">
@@ -712,6 +815,30 @@
         <v>3.1576511773077501E-3</v>
       </c>
       <c r="H5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="1">
+        <v>14.933638574329001</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1.36974892704846</v>
+      </c>
+      <c r="O5" s="1">
+        <v>-3.77738387675406E-3</v>
+      </c>
+      <c r="P5" s="1">
+        <v>4.9674346189836603E-4</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>2.3751416237725098</v>
+      </c>
+      <c r="R5" s="1">
+        <v>40.0953848602744</v>
+      </c>
+      <c r="S5" s="1">
+        <v>3.1530358049070501E-3</v>
+      </c>
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:22" ht="42.75">
@@ -737,6 +864,30 @@
         <v>2.2873004957297801E-3</v>
       </c>
       <c r="H6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="1">
+        <v>14.724938429333699</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1.3807434647299901</v>
+      </c>
+      <c r="O6" s="1">
+        <v>-3.6091407910026898E-3</v>
+      </c>
+      <c r="P6" s="1">
+        <v>5.0284648875260104E-4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>2.3756218665706101</v>
+      </c>
+      <c r="R6" s="1">
+        <v>39.794085120188598</v>
+      </c>
+      <c r="S6" s="1">
+        <v>3.0595718540740698E-3</v>
+      </c>
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:22" ht="42.75">
@@ -762,6 +913,30 @@
         <v>2.2873004957154699E-3</v>
       </c>
       <c r="H7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="1">
+        <v>14.8057635352784</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1.37912253903686</v>
+      </c>
+      <c r="O7" s="1">
+        <v>-3.4188647193036099E-3</v>
+      </c>
+      <c r="P7" s="1">
+        <v>7.1982111569123496E-4</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2.3743525633050599</v>
+      </c>
+      <c r="R7" s="1">
+        <v>40.9379263375221</v>
+      </c>
+      <c r="S7" s="1">
+        <v>3.7295390659607699E-3</v>
+      </c>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:22" ht="42.75">
@@ -787,6 +962,30 @@
         <v>2.3832613509317101E-3</v>
       </c>
       <c r="H8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="1">
+        <v>14.8433449204122</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1.3747228736222801</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-3.6570498031116101E-3</v>
+      </c>
+      <c r="P8" s="1">
+        <v>4.5224198601142202E-4</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>2.3749768015384198</v>
+      </c>
+      <c r="R8" s="1">
+        <v>40.936177042228799</v>
+      </c>
+      <c r="S8" s="1">
+        <v>3.2879580476745099E-3</v>
+      </c>
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:22" ht="42.75">
@@ -812,6 +1011,30 @@
         <v>3.80546338785298E-3</v>
       </c>
       <c r="H9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="1">
+        <v>14.842235301195901</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1.37395457637812</v>
+      </c>
+      <c r="O9" s="1">
+        <v>-3.5799837673718901E-3</v>
+      </c>
+      <c r="P9" s="1">
+        <v>3.3003620537021798E-4</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>2.3746620129962501</v>
+      </c>
+      <c r="R9" s="1">
+        <v>39.826768100090803</v>
+      </c>
+      <c r="S9" s="1">
+        <v>2.7649563976547202E-3</v>
+      </c>
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:22" ht="42.75">
@@ -837,6 +1060,30 @@
         <v>3.0226167595771699E-3</v>
       </c>
       <c r="H10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="1">
+        <v>14.7140534867903</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1.3722287407698199</v>
+      </c>
+      <c r="O10" s="1">
+        <v>-4.6867562452318802E-3</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1.53256610682857E-3</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2.3770253157935</v>
+      </c>
+      <c r="R10" s="1">
+        <v>39.861430850535399</v>
+      </c>
+      <c r="S10" s="1">
+        <v>4.5746009913729801E-3</v>
+      </c>
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:22" ht="42.75">
@@ -862,6 +1109,30 @@
         <v>2.2873004957157999E-3</v>
       </c>
       <c r="H11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="1">
+        <v>14.983450865795399</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1.36670341457898</v>
+      </c>
+      <c r="O11" s="1">
+        <v>-3.8595361224924799E-3</v>
+      </c>
+      <c r="P11" s="1">
+        <v>3.6668735644375898E-4</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2.3748885820873502</v>
+      </c>
+      <c r="R11" s="1">
+        <v>39.8873720168422</v>
+      </c>
+      <c r="S11" s="1">
+        <v>2.90399839449264E-3</v>
+      </c>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:22" ht="42.75">
@@ -887,6 +1158,30 @@
         <v>2.2873004957070001E-3</v>
       </c>
       <c r="H12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="1">
+        <v>14.676652845174701</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1.36305987055036</v>
+      </c>
+      <c r="O12" s="1">
+        <v>-2.5380445351778501E-3</v>
+      </c>
+      <c r="P12" s="1">
+        <v>7.2330641435824905E-4</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2.3748144903928901</v>
+      </c>
+      <c r="R12" s="1">
+        <v>40.033403360007497</v>
+      </c>
+      <c r="S12" s="1">
+        <v>3.88038111634588E-3</v>
+      </c>
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:22" ht="42.75">
@@ -912,6 +1207,30 @@
         <v>2.28730095364079E-3</v>
       </c>
       <c r="H13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="1">
+        <v>14.8877937459382</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1.3673741249147899</v>
+      </c>
+      <c r="O13" s="1">
+        <v>-3.7350176739204899E-3</v>
+      </c>
+      <c r="P13" s="1">
+        <v>3.7679071748980401E-4</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>2.3744312338474698</v>
+      </c>
+      <c r="R13" s="1">
+        <v>40.047295240257498</v>
+      </c>
+      <c r="S13" s="1">
+        <v>2.8729325603818298E-3</v>
+      </c>
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:22" ht="42.75">
@@ -937,6 +1256,30 @@
         <v>2.5673002158590401E-3</v>
       </c>
       <c r="H14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="1">
+        <v>15.004536995555</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1.36964757866019</v>
+      </c>
+      <c r="O14" s="1">
+        <v>-3.7588647764971502E-3</v>
+      </c>
+      <c r="P14" s="1">
+        <v>3.0015645823934701E-4</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>2.3748226969765298</v>
+      </c>
+      <c r="R14" s="1">
+        <v>41.145869310003199</v>
+      </c>
+      <c r="S14" s="1">
+        <v>2.8461837569993499E-3</v>
+      </c>
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:22" ht="42.75">
@@ -962,6 +1305,30 @@
         <v>2.7664408588178899E-3</v>
       </c>
       <c r="H15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="1">
+        <v>14.731519728181899</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1.3678744652934101</v>
+      </c>
+      <c r="O15" s="1">
+        <v>-3.7173313927009299E-3</v>
+      </c>
+      <c r="P15" s="1">
+        <v>3.9752505513142701E-4</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>2.3746123640643799</v>
+      </c>
+      <c r="R15" s="1">
+        <v>40.066889050143402</v>
+      </c>
+      <c r="S15" s="1">
+        <v>3.1924114201463201E-3</v>
+      </c>
       <c r="T15" s="1"/>
     </row>
     <row r="16" spans="1:22" ht="42.75">
@@ -987,6 +1354,30 @@
         <v>2.9722505738732398E-3</v>
       </c>
       <c r="H16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="1">
+        <v>14.625208533355</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1.37000820344151</v>
+      </c>
+      <c r="O16" s="1">
+        <v>-3.75844712472864E-3</v>
+      </c>
+      <c r="P16" s="1">
+        <v>4.6651932019780201E-4</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>2.3750217374632601</v>
+      </c>
+      <c r="R16" s="1">
+        <v>40.064203200042698</v>
+      </c>
+      <c r="S16" s="1">
+        <v>3.0765220069264498E-3</v>
+      </c>
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" ht="42.75">
@@ -1012,6 +1403,30 @@
         <v>3.7606322378712399E-3</v>
       </c>
       <c r="H17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="1">
+        <v>14.558821600230299</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1.3694786179946401</v>
+      </c>
+      <c r="O17" s="1">
+        <v>-3.5424763002060702E-3</v>
+      </c>
+      <c r="P17" s="1">
+        <v>4.2424058510097699E-4</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>2.3743230739167398</v>
+      </c>
+      <c r="R17" s="1">
+        <v>40.062751910001602</v>
+      </c>
+      <c r="S17" s="1">
+        <v>2.9556488550297202E-3</v>
+      </c>
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" ht="42.75">
@@ -1037,6 +1452,30 @@
         <v>3.00948135623051E-3</v>
       </c>
       <c r="H18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="1">
+        <v>14.790762506968401</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1.3699569197905901</v>
+      </c>
+      <c r="O18" s="1">
+        <v>-2.66302127231713E-3</v>
+      </c>
+      <c r="P18" s="1">
+        <v>6.9485211078476605E-4</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>2.3758661519128399</v>
+      </c>
+      <c r="R18" s="1">
+        <v>40.092184980151103</v>
+      </c>
+      <c r="S18" s="1">
+        <v>3.12992585445972E-3</v>
+      </c>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" ht="42.75">
@@ -1062,6 +1501,30 @@
         <v>3.2666807801508E-3</v>
       </c>
       <c r="H19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="1">
+        <v>14.5857901705748</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1.3743157146796501</v>
+      </c>
+      <c r="O19" s="1">
+        <v>-3.6440990410240002E-3</v>
+      </c>
+      <c r="P19" s="1">
+        <v>4.1887839852329002E-4</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>2.3756083800533099</v>
+      </c>
+      <c r="R19" s="1">
+        <v>40.066224732261801</v>
+      </c>
+      <c r="S19" s="1">
+        <v>3.3162969271159199E-3</v>
+      </c>
     </row>
     <row r="20" spans="1:20" ht="42.75">
       <c r="A20" s="1" t="s">
@@ -1086,6 +1549,30 @@
         <v>3.1293293069413501E-3</v>
       </c>
       <c r="H20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="1">
+        <v>14.824045703012899</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1.37075775151811</v>
+      </c>
+      <c r="O20" s="1">
+        <v>-3.8150241749168598E-3</v>
+      </c>
+      <c r="P20" s="1">
+        <v>3.8270076853579401E-4</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>2.3763310394269599</v>
+      </c>
+      <c r="R20" s="1">
+        <v>40.0567703200118</v>
+      </c>
+      <c r="S20" s="1">
+        <v>2.67135783702148E-3</v>
+      </c>
     </row>
     <row r="21" spans="1:20" ht="42.75">
       <c r="A21" s="1" t="s">
@@ -1110,6 +1597,30 @@
         <v>3.2773943326162101E-3</v>
       </c>
       <c r="H21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" s="1">
+        <v>14.6997126302309</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1.3685211862944999</v>
+      </c>
+      <c r="O21" s="1">
+        <v>-2.7118019795334299E-3</v>
+      </c>
+      <c r="P21" s="1">
+        <v>7.8306075113120197E-4</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>2.3747370044842202</v>
+      </c>
+      <c r="R21" s="1">
+        <v>40.035677200001601</v>
+      </c>
+      <c r="S21" s="1">
+        <v>3.8396871321444499E-3</v>
+      </c>
     </row>
     <row r="22" spans="1:20" ht="42.75">
       <c r="A22" s="1" t="s">
@@ -1134,6 +1645,30 @@
         <v>2.2873004957078098E-3</v>
       </c>
       <c r="H22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1">
+        <v>14.8389165862786</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1.3710932691136699</v>
+      </c>
+      <c r="O22" s="1">
+        <v>-3.85109006763474E-3</v>
+      </c>
+      <c r="P22" s="1">
+        <v>3.6465655170874497E-4</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>2.3746602910082601</v>
+      </c>
+      <c r="R22" s="1">
+        <v>41.198491750700697</v>
+      </c>
+      <c r="S22" s="1">
+        <v>3.1387096096309E-3</v>
+      </c>
     </row>
     <row r="23" spans="1:20" ht="42.75">
       <c r="A23" s="1" t="s">
@@ -1158,6 +1693,30 @@
         <v>2.3563193049736799E-3</v>
       </c>
       <c r="H23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="1">
+        <v>14.699979997150701</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1.3719132957222</v>
+      </c>
+      <c r="O23" s="1">
+        <v>-3.85958021243952E-3</v>
+      </c>
+      <c r="P23" s="1">
+        <v>6.0744265950530001E-4</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>2.3749411769019599</v>
+      </c>
+      <c r="R23" s="1">
+        <v>40.120789420031699</v>
+      </c>
+      <c r="S23" s="1">
+        <v>3.6527369043079902E-3</v>
+      </c>
     </row>
     <row r="24" spans="1:20" ht="42.75">
       <c r="A24" s="1" t="s">
@@ -1182,6 +1741,30 @@
         <v>2.2873004957038802E-3</v>
       </c>
       <c r="H24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" s="1">
+        <v>14.850825784730301</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1.37629282448768</v>
+      </c>
+      <c r="O24" s="1">
+        <v>-3.50645796181886E-3</v>
+      </c>
+      <c r="P24" s="1">
+        <v>7.0031802978287898E-4</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>2.3740508791747601</v>
+      </c>
+      <c r="R24" s="1">
+        <v>40.120129490438401</v>
+      </c>
+      <c r="S24" s="1">
+        <v>3.5621574613764698E-3</v>
+      </c>
     </row>
     <row r="25" spans="1:20" ht="42.75">
       <c r="A25" s="1" t="s">
@@ -1206,6 +1789,30 @@
         <v>2.2873004957016498E-3</v>
       </c>
       <c r="H25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="1">
+        <v>14.670319134048301</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1.3738876642660001</v>
+      </c>
+      <c r="O25" s="1">
+        <v>-3.4851377922430599E-3</v>
+      </c>
+      <c r="P25" s="1">
+        <v>4.8695532138430601E-4</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>2.3749648190085599</v>
+      </c>
+      <c r="R25" s="1">
+        <v>40.134249210000497</v>
+      </c>
+      <c r="S25" s="1">
+        <v>3.0446420330517599E-3</v>
+      </c>
     </row>
     <row r="26" spans="1:20" ht="42.75">
       <c r="A26" s="1" t="s">
@@ -1230,6 +1837,30 @@
         <v>2.5765476756944902E-3</v>
       </c>
       <c r="H26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M26" s="1">
+        <v>14.4932987574155</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1.3743278776875201</v>
+      </c>
+      <c r="O26" s="1">
+        <v>-3.0723009424214998E-3</v>
+      </c>
+      <c r="P26" s="1">
+        <v>7.9600177262882698E-4</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>2.3748421171457399</v>
+      </c>
+      <c r="R26" s="1">
+        <v>40.140833600038803</v>
+      </c>
+      <c r="S26" s="1">
+        <v>3.8989459643780501E-3</v>
+      </c>
     </row>
     <row r="27" spans="1:20" ht="42.75">
       <c r="A27" s="1" t="s">
@@ -1254,6 +1885,30 @@
         <v>3.38119583309008E-3</v>
       </c>
       <c r="H27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" s="1">
+        <v>14.716675101967301</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1.3803443937914199</v>
+      </c>
+      <c r="O27" s="1">
+        <v>-3.5041615750560501E-3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>5.6951307497084605E-4</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>2.3754158286973701</v>
+      </c>
+      <c r="R27" s="1">
+        <v>40.116778040000099</v>
+      </c>
+      <c r="S27" s="1">
+        <v>3.3892285182225601E-3</v>
+      </c>
     </row>
     <row r="28" spans="1:20" ht="42.75">
       <c r="A28" s="1" t="s">
@@ -1278,6 +1933,30 @@
         <v>2.2873004957283298E-3</v>
       </c>
       <c r="H28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="1">
+        <v>14.7865656532696</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1.3814539815623801</v>
+      </c>
+      <c r="O28" s="1">
+        <v>-3.5900625334002799E-3</v>
+      </c>
+      <c r="P28" s="1">
+        <v>2.6859234528321598E-4</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>2.37466815877695</v>
+      </c>
+      <c r="R28" s="1">
+        <v>40.075859727511002</v>
+      </c>
+      <c r="S28" s="1">
+        <v>2.88942666959557E-3</v>
+      </c>
     </row>
     <row r="29" spans="1:20" ht="42.75">
       <c r="A29" s="1" t="s">
@@ -1302,6 +1981,30 @@
         <v>2.4042735617825898E-3</v>
       </c>
       <c r="H29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M29" s="1">
+        <v>14.721736741178701</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1.3801705087021201</v>
+      </c>
+      <c r="O29" s="1">
+        <v>-3.7188642891489501E-3</v>
+      </c>
+      <c r="P29" s="1">
+        <v>6.2834482166534695E-4</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>2.3750390168334001</v>
+      </c>
+      <c r="R29" s="1">
+        <v>40.091726580007901</v>
+      </c>
+      <c r="S29" s="1">
+        <v>3.3432688062379999E-3</v>
+      </c>
     </row>
     <row r="30" spans="1:20" ht="42.75">
       <c r="A30" s="1" t="s">
@@ -1326,6 +2029,30 @@
         <v>2.2873004957217201E-3</v>
       </c>
       <c r="H30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="1">
+        <v>14.8048373114146</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1.3836970543293701</v>
+      </c>
+      <c r="O30" s="1">
+        <v>-3.55138990558073E-3</v>
+      </c>
+      <c r="P30" s="1">
+        <v>5.2271857294870696E-4</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>2.37486792529169</v>
+      </c>
+      <c r="R30" s="1">
+        <v>39.707268290055303</v>
+      </c>
+      <c r="S30" s="1">
+        <v>3.0080210043196901E-3</v>
+      </c>
     </row>
     <row r="31" spans="1:20" ht="42.75">
       <c r="A31" s="1" t="s">
@@ -1350,6 +2077,30 @@
         <v>2.2873004957083901E-3</v>
       </c>
       <c r="H31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M31" s="1">
+        <v>14.729578883481601</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1.3830240715550299</v>
+      </c>
+      <c r="O31" s="1">
+        <v>-4.2437939183158696E-3</v>
+      </c>
+      <c r="P31" s="1">
+        <v>-1.5166555182818901E-4</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>2.37509266936868</v>
+      </c>
+      <c r="R31" s="1">
+        <v>39.712873250011803</v>
+      </c>
+      <c r="S31" s="1">
+        <v>2.2873004957014199E-3</v>
+      </c>
     </row>
     <row r="32" spans="1:20" ht="42.75">
       <c r="A32" s="1" t="s">
@@ -1374,8 +2125,32 @@
         <v>2.28730049570141E-3</v>
       </c>
       <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" ht="42.75">
+      <c r="L32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M32" s="1">
+        <v>14.7880280563038</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1.3807511366098499</v>
+      </c>
+      <c r="O32" s="1">
+        <v>-3.6234581140455698E-3</v>
+      </c>
+      <c r="P32" s="1">
+        <v>4.2751152495895699E-4</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>2.3760703570380399</v>
+      </c>
+      <c r="R32" s="1">
+        <v>39.7541409100062</v>
+      </c>
+      <c r="S32" s="1">
+        <v>2.62505258179596E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="42.75">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -1398,6 +2173,30 @@
         <v>2.28730049855782E-3</v>
       </c>
       <c r="H33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M33" s="1">
+        <v>14.7458143243305</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.3797157584905799</v>
+      </c>
+      <c r="O33" s="1">
+        <v>-3.5831549458077102E-3</v>
+      </c>
+      <c r="P33" s="1">
+        <v>5.9630831214409804E-4</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>2.37560824904658</v>
+      </c>
+      <c r="R33" s="1">
+        <v>39.774286210007901</v>
+      </c>
+      <c r="S33" s="1">
+        <v>3.0785269283661498E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
